--- a/wcca_cases.xlsx
+++ b/wcca_cases.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,7 +27,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -36,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,7 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -77,9 +81,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -442,15 +449,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -471,15 +477,10 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Caption</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Caption</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Search Term</t>
         </is>
@@ -503,17 +504,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>J.G. Wentworth Originations, LLC vs. None</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. None</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -535,17 +531,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>J.G. Wentworth Originations, LLC vs. Kailyun Jackson</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. Kailyun Jackson</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -567,17 +558,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Vilas</t>
+          <t>J.G. Wentworth Originations, LLC vs. None</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. None</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -599,17 +585,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>J.G. Wentworth Originations, LLC vs. Shanika Haynes</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. Shanika Haynes</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -631,17 +612,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>J.G. Wentworth Originations, LLC vs. None</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. None</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -663,17 +639,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>J.G. Wentworth Originations, LLC vs. Ethel Smith</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. Ethel Smith</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -695,17 +666,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>La Crosse</t>
+          <t>J.G. Wentworth Originations, LLC vs. None</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. None</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -727,17 +693,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>J.G. Wentworth Originations, LLC vs. Briana Williams</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. Briana Williams</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -759,17 +720,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Burnett</t>
+          <t>In re: Petition for Approval of Transfer of Payment Rights from Evea Hermann to J.G. Wentworth Originations, LLC</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>In re: Petition for Approval of Transfer of Payment Rights from Evea Hermann to J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
@@ -791,47 +747,37 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>J.G. Wentworth Originations, LLC vs. Tyler Dix</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>J.G. Wentworth Originations, LLC vs. Tyler Dix</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth</t>
+          <t>JG Wentworth</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026CV005499</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>06-10-2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Peachtree Settlement Funding, LLC vs. Carol D'Aquisto</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Peachtree Settlement</t>
         </is>
@@ -855,405 +801,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Sheboygan</t>
+          <t>Peachtree Settlement Funding, LLC vs. none</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Peachtree Settlement Funding, LLC vs. none</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
           <t>Peachtree Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026TR002983</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>06-09-2026</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Jefferson</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Jefferson</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. Emily Madison Lasko</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026FO000375</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>05-27-2026</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Walworth</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Walworth</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. Rene N Laskosz</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026SC000306</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>05-12-2026</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Portage</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Portage</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>H10 LLC vs. Joseph Eberling et al</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026SC000305</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>05-11-2026</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Portage</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Portage</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>H10 LLC vs. Elizabeth Schulze et al</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026TR002234</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>05-01-2026</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Jefferson</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Jefferson</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Jefferson, County of vs. Jeffrey Alan Laskowski</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026CT000420</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>06-09-2026</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Dane</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Dane</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. William J Legere</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Legere</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026SC002171</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>05-14-2026</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Heights Finance Corporation vs. William J. Legere</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Legere</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026TR002427</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>05-06-2026</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Fond du Lac</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Fond du Lac</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Fond du Lac, County of vs. William J Legere</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Legere</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026CT000376</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>05-06-2026</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Fond du Lac</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Fond du Lac</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. William J Legere</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Legere</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2026CT000351</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>04-22-2026</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Outagamie</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Outagamie</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. William Joseph Legere</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Legere</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026TR002775</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>05-26-2026</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Dunn</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Dunn</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>State of Wisconsin vs. Rony F Tenemaza Zhunio</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>T ENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2026SC013796</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>05-21-2026</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>TENERIFFE HOLDINGS LLC vs. Robert A. Flowers et al</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>T ENE</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="8"/>
 </worksheet>
 </file>